--- a/pacjenci/LUDWIK KOZINA.xlsx
+++ b/pacjenci/LUDWIK KOZINA.xlsx
@@ -483,10 +483,14 @@
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Aktywna choroba</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -538,17 +542,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4 - wychwyt umiarkowanie większy od wątroby</t>
+          <t>4 - utrzymujący się wychwyt patologiczny</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Częściowa odpowiedź metaboliczna na leczenie. Klasyfikacja Lugano: Partial Response (PR) - częściowa odpowiedź na leczenie. Deauville: 4 - wychwyt umiarkowanie większy od wątroby.</t>
+          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
         </is>
       </c>
     </row>

--- a/pacjenci/LUDWIK KOZINA.xlsx
+++ b/pacjenci/LUDWIK KOZINA.xlsx
@@ -413,323 +413,242 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>24.05.2021</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Chłoniak ziarniczy. Ocena stopnia zaawansowania.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po  64min od podania 18F-FDG. Glikemia: 124mg%</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Aktywne metabolicznie węzły chłonne po stronie lewej: - grupy 2 średnicy wg PET do 25mm, SUV max do 6,1, - grupy 3 średnicy wg PET do 10mm, SUV max do 3,6, - grupy 4 średnicy wg PET do 12mm, SUV max do 4,5, - grupy 5 średnicy wg PET do 12mm, SUV max do 3,0, - podobojczykowe średnicy wg PET do 10mm, SUV max do 3,0. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Polipowate pogrubienie błony śluzowej lewej zatoki szczękowej.  Klatka piersiowa i śródpiersie: Aktywne metabolicznie spakietowane i pojedyncze węzły chłonne:  - pachy lewej i międzypiersiowe lewe średnicy wg PET do 34mm, SUV max do 7,9, - podostrogowe po stronie prawej średnicy wg PET do 12mm, SUV max do 3,6, - wnęka płuca prawego, SUV max 2,8. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły pachy prawej średnicy do 12mm (SUV max do 1,5).  Brzuch i miednica: Aktywny metabolicznie węzeł chłonny przyaortalny prawy położony powyżej pnia trzewnego średnicy wg PET 15mm, SUV max 7,7. Mierna, rozlana aktywność metaboliczna w topografii ścian żołądka, SUV max do 4,0 - w pierwszej kolejności czynnościowa. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Guzek trzonu nadnercza prawego średnicy 11mm.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Dyskopatia L5/S1. Masywne osteofity na przednich krawędziach trzonów C3/4.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax 1,7, Prawy płat wątroby SUVmax do 2,8.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aktywna choroba</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono aktywny metabolicznie proces chłoniakowy z zajęciem węzłów chłonnych po obu stronach przepony.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>7.9</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>03.08.2021</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina. Ocena po dwóch cyklach ABVD.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 87mg%.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Rozlanie wzmożony metabolizm FDG w topografii przedniej części dna jamy ustnej/języka, SUV max do 12,9 - do kontroli miejscowej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Nieaktywne metabolicznie węzły chłonne szyjne po stronie lewej wielkości do 14x10mm [największe nadobojczykowe]. Polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej, wielkości 17mm.  Klatka piersiowa i śródpiersie: Miernie pobudzone metabolicznie pojedyncze i spakietowane węzły chłonne pachowe i międzypiersiowe lewe, wielkości do 34x25mm, SUV max do 1,9 Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne pachowe prawe, wielkości do 10mm Węzły chłonne podobojczykowe wielkości do 11mm. Węzły chłonne podostrogowe wielkości do 12mm. Niewielki obszar zmian miąższowo-włóknistych w segm. 4 płuca lewego. Gorsze upowietrznienie miąższu płucnego i niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Rozlanie wzmożona aktywność metaboliczna w topografii ścian żołądka i XII-icy, SUV max do 4,8 - w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Niewielkie pogrubienie trzonu nadnercza prawego oraz nieco większe lewego. Nieliczne drobne węzły chłonne przyaortalne. Drobne zwapnienie w lewym płacie niepowiększonej prostaty.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Masywne osteofity na przednich krawędziach trzonów kręgowych C3 i C4. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa - ciasna na poziomie L5/S1. Os sacrum arcuatum. Drobne zmiany wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i wydatniejsze w stawach żebrowo-poprzecznych.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax 1,8; Prawy płat wątroby SUVmax do 3,2.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono dobrą odpowiedź metaboliczną choroby chłoniakowej na stosowane leczenie z częściową regresją radiologiczną zmian.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>12.9</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>17.02.2022</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina. Ocena po zakończeniu I serii chemioterapii 8 cykli ABVD.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57 min od podania 18F-FDG. Glikemia: 120 mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Wzmożony metabolizm FDG w topografii nosogardła SUV max do 3,6 oraz w przedniej części prawego fałdu głosowego SUV max do 3,6- do kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja lewej zatoki czołowej. Wydatne zgrubienia błony śluzowej w sitowiu tylnym, lewym. Polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej, wielkości 20mm.  Klatka piersiowa i śródpiersie: Miernie pobudzone metabolicznie węzły chłonne pachowe lewe wielkości do 23x20 mm SUV max do 1,8. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne podostrogowe wielkości do 13 mm. Niewielki obszar zmian miąższowo-włóknistych w segm. 4 płuca lewego. Gorsze upowietrznienie miąższu płucnego i niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Aktywny metabolicznie węzeł chłonny  okołoaortalny prawy  na poziomie kręgu L1 średnicy 13 mm SUV max 4,1 [Im fuz. 172]. Rozlanie wzmożony metabolizm FDG w żołądku SUV max do 4,0- w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Niewielkie pogrubienie trzonu nadnercza prawego oraz nieco większe lewego. Drobne zwapnienie w lewym płacie niepowiększonej prostaty.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Masywne osteofity na przednich krawędziach trzonów kręgowych C3 i C4. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa - ciasna na poziomie L5/S1 [ze sklerotyczną przebudową blaszek granicznych i przyległych części trzonów kręgowych - typu Modic 3]. Os sacrum arcuatum. Drobne zmiany wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i wydatniejsze w stawach żebrowo-poprzecznych. Ok. 5mm wyspa kostna w głowie prawej kości udowej.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax 1,2 Prawy płat wątroby SUVmax do 2,6</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność pojedynczego aktywnego metabolicznie węzła chłonnego okołoaortalnego prawego na poziomie L1- wznowa choroby chłoniakowej (lokalizacja węzła jak w PET/CT wyjściowym z 24.05.2021). Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>4.1</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>12.05.2022</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina. Ocena po 8 cyklach ABVD.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57 min od podania 18F-FDG. Glikemia: 105mg%.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Wzmożony metabolizm FDG w topografii nosogardła SUV max do 3,6 oraz w przedniej części prawego fałdu głosowego SUV max do 3,6- do kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja lewej zatoki czołowej. Polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej, wielkości 16mm. Miernie powiększona tarczyca, zwłaszcza w zakresie prawego płata - do kontroli w USG.  Klatka piersiowa i śródpiersie: Miernie pobudzone metabolicznie węzły chłonne pachowe lewe, drobne prawe wielkości do 15 mm SUV max do 1,5. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne podostrogowe i przytchawicze dolne prawe wielkości do 13 mm. Drobne obwodowe pęcherze rozedmowe w płacie górnym płuca prawego. Gorsze upowietrznienie miąższu płucnego i niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Aktywny metabolicznie węzeł chłonny okołoaortalny prawy  na poziomie kręgu L1 wielkości 31x25 mm SUV max 6,7 [Im fuz. 169]. Pobudzenie metaboliczne w żołądku - w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Niewielkie pogrubienie trzonu nadnercza prawego oraz nieco większe lewego - do 17mm. Drobne zwapnienie w lewym płacie niepowiększonej prostaty. Niewielkie wodniaki obu jąder.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Masywne osteofity na przednich krawędziach trzonów kręgowych C3 i C4. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa - ciasna na poziomie L5/S1 [ze sklerotyczną przebudową blaszek granicznych i przyległych części trzonów kręgowych - typu Modic 3]. Os sacrum arcuatum. Drobne zmiany wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i wydatniejsze w stawach żebrowo-poprzecznych. Ok. 5mm wyspa kostna w głowie prawej kości udowej.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax 1,5; Prawy płat wątroby SUVmax do 2,0.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność pojedynczego aktywnego metabolicznie węzła chłonnego okołoaortalnego prawego na poziomie L1- wznowa choroby chłoniakowej - w porównaniu do badania z 17.02.2022 progresja. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>6.7</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>PD</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5 - znacznie zwiększony wychwyt lub nowe zmiany</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Progresja choroby. Klasyfikacja Lugano: Progressive Disease (PD) - progresja choroby. Deauville: 5 - znacznie zwiększony wychwyt lub nowe zmiany.</t>
-        </is>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>17.10.2022</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina. Po 8 cyklach ABVD. Ocena po radioterapii.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57 min od podania 18F-FDG. Glikemia: 92mg%.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Wzmożony metabolizm FDG w topografii przedniej części podniebienia oraz nieco nosogardła i przedniej części prawego fałdu głosowego, SUV max do 3,9- do ew. kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja lewej zatoki czołowej. Polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej, wielkości 16mm. Miernie powiększona tarczyca, zwłaszcza w zakresie prawego płata - do kontroli w USG.  Klatka piersiowa i śródpiersie: Miernie pobudzone metabolicznie węzły chłonne pachowe lewe,  wielkości do 16x13 mm, SUV max do 1,6 oraz drobne prawe. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne podostrogowe i przytchawicze dolne prawe wielkości do 12 mm. Drobne obwodowe pęcherze rozedmowe w płacie górnym płuca prawego. Niewielkie zmiany miąższowe nadprzeponowo po stronie lewej. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Aktywny metabolicznie węzeł chłonny okołoaortalny prawy,  na poziomie kręgu L1 wielkości 34x28 mm SUV max 8,1 [Im fuz. 172]. Pobudzenie metaboliczne w żołądku oraz okrężnicy zstępującej  - w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Niewielkie pogrubienie trzonów obu nadnerczy. Drobne zwapnienie w lewym płacie niepowiększonej prostaty. Niewielkie wodniaki obu jąder.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Masywne osteofity na przednich krawędziach trzonów kręgowych C3 i C4. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa - ciasna na poziomie L5/S1 [ze sklerotyczną przebudową blaszek granicznych i przyległych części trzonów kręgowych - typu Modic 3]. Os sacrum arcuatum. Drobne zmiany wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i wydatniejsze w stawach żebrowo-poprzecznych. Ok. 5mm wyspa kostna w głowie prawej kości udowej.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax 2,0; Prawy płat wątroby SUVmax do 2,6.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność pojedynczego aktywnego metabolicznie węzła chłonnego okołoaortalnego prawego na poziomie L1- wznowa choroby chłoniakowej - w porównaniu do badania z 12.05.2022 dalsza progresja wielkości. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>8.1</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>PD</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5 - znacznie zwiększony wychwyt lub nowe zmiany</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Progresja choroby. Klasyfikacja Lugano: Progressive Disease (PD) - progresja choroby. Deauville: 5 - znacznie zwiększony wychwyt lub nowe zmiany.</t>
-        </is>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>22.12.2022</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>6</v>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina. Po 8 cyklach ABVD. Ocena po 2 cyklach BGD.</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  56 min od podania 18F-FDG. Glikemia: 125mg%.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Wzmożony metabolizm FDG w topografii przedniej części podniebienia oraz nieco nosogardła i przedniej części prawego fałdu głosowego, SUV max do 3,8- do ew. kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja lewej zatoki czołowej. Polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej, wielkości 16mm. Miernie powiększona tarczyca, zwłaszcza w zakresie prawego płata - do kontroli w USG.  Klatka piersiowa i śródpiersie: Miernie pobudzone metabolicznie węzły chłonne pachowe lewe,  wielkości do 16x13 mm, SUV max do 1,4 oraz drobne prawe. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne podostrogowe i przytchawicze dolne prawe wielkości do 12 mm. Drobne obwodowe pęcherze rozedmowe w płacie górnym płuca prawego. Niewielkie zmiany miąższowe nadprzeponowo po stronie lewej. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Aktywny metabolicznie węzeł chłonny okołoaortalny prawy, na poziomie kręgu L1 wielkości 37x28 mm (poprzednio 34x28 mm) SUV max 6,0 (poprzednio SUV max 8,1) [Im fuz. 177]. Pobudzenie metaboliczne w żołądku oraz okrężnicy zstępującej  - w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Niewielkie pogrubienie trzonów obu nadnerczy. Drobne zwapnienie w lewym płacie niepowiększonej prostaty. Niewielkie wodniaki obu jąder.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Masywne osteofity na przednich krawędziach trzonów kręgowych C3 i C4. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa - ciasna na poziomie L5/S1 [ze sklerotyczną przebudową blaszek granicznych i przyległych części trzonów kręgowych - typu Modic 3]. Os sacrum arcuatum. Drobne zmiany wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i wydatniejsze w stawach żebrowo-poprzecznych. Ok. 5mm wyspa kostna w głowie prawej kości udowej.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax 2,0; Prawy płat wątroby SUVmax do 2,4.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność pojedynczego aktywnego metabolicznie węzła chłonnego okołoaortalnego prawego na poziomie L1- wznowa choroby chłoniakowej - w porównaniu do badania z 17.10.2022 obraz PET/CT z 18F-FDG nie uległ zasadniczej zmianie. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>8.1</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/LUDWIK KOZINA.xlsx
+++ b/pacjenci/LUDWIK KOZINA.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po  64min od podania 18F-FDG. Glikemia: 124mg%</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Aktywne metabolicznie węzły chłonne po stronie lewej: - grupy 2 średnicy wg PET do 25mm, SUV max do 6,1, - grupy 3 średnicy wg PET do 10mm, SUV max do 3,6, - grupy 4 średnicy wg PET do 12mm, SUV max do 4,5, - grupy 5 średnicy wg PET do 12mm, SUV max do 3,0, - podobojczykowe średnicy wg PET do 10mm, SUV max do 3,0. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Polipowate pogrubienie błony śluzowej lewej zatoki szczękowej.  Klatka piersiowa i śródpiersie: Aktywne metabolicznie spakietowane i pojedyncze węzły chłonne:  - pachy lewej i międzypiersiowe lewe średnicy wg PET do 34mm, SUV max do 7,9, - podostrogowe po stronie prawej średnicy wg PET do 12mm, SUV max do 3,6, - wnęka płuca prawego, SUV max 2,8. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły pachy prawej średnicy do 12mm (SUV max do 1,5).  Brzuch i miednica: Aktywny metabolicznie węzeł chłonny przyaortalny prawy położony powyżej pnia trzewnego średnicy wg PET 15mm, SUV max 7,7. Mierna, rozlana aktywność metaboliczna w topografii ścian żołądka, SUV max do 4,0 - w pierwszej kolejności czynnościowa. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Guzek trzonu nadnercza prawego średnicy 11mm.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Dyskopatia L5/S1. Masywne osteofity na przednich krawędziach trzonów C3/4.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax 1,7, Prawy płat wątroby SUVmax do 2,8.</t>
+          <t>124</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne po stronie lewej: - grupy 2 średnicy wg PET do 25mm, SUV max do 6,1, - grupy 3 średnicy wg PET do 10mm, SUV max do 3,6, - grupy 4 średnicy wg PET do 12mm, SUV max do 4,5, - grupy 5 średnicy wg PET do 12mm, SUV max do 3,0, - podobojczykowe średnicy wg PET do 10mm, SUV max do 3,0. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Polipowate pogrubienie błony śluzowej lewej zatoki szczękowej.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie spakietowane i pojedyncze węzły chłonne:  - pachy lewej i międzypiersiowe lewe średnicy wg PET do 34mm, SUV max do 7,9, - podostrogowe po stronie prawej średnicy wg PET do 12mm, SUV max do 3,6, - wnęka płuca prawego, SUV max 2,8. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły pachy prawej średnicy do 12mm (SUV max do 1,5).</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie węzeł chłonny przyaortalny prawy położony powyżej pnia trzewnego średnicy wg PET 15mm, SUV max 7,7. Mierna, rozlana aktywność metaboliczna w topografii ścian żołądka, SUV max do 4,0 - w pierwszej kolejności czynnościowa. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Guzek trzonu nadnercza prawego średnicy 11mm.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Dyskopatia L5/S1. Masywne osteofity na przednich krawędziach trzonów C3/4.  Inne: Miażdżyca aorty i tętnic potomnych.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono aktywny metabolicznie proces chłoniakowy z zajęciem węzłów chłonnych po obu stronach przepony.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>7.9</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 87mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Rozlanie wzmożony metabolizm FDG w topografii przedniej części dna jamy ustnej/języka, SUV max do 12,9 - do kontroli miejscowej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Nieaktywne metabolicznie węzły chłonne szyjne po stronie lewej wielkości do 14x10mm [największe nadobojczykowe]. Polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej, wielkości 17mm.  Klatka piersiowa i śródpiersie: Miernie pobudzone metabolicznie pojedyncze i spakietowane węzły chłonne pachowe i międzypiersiowe lewe, wielkości do 34x25mm, SUV max do 1,9 Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne pachowe prawe, wielkości do 10mm Węzły chłonne podobojczykowe wielkości do 11mm. Węzły chłonne podostrogowe wielkości do 12mm. Niewielki obszar zmian miąższowo-włóknistych w segm. 4 płuca lewego. Gorsze upowietrznienie miąższu płucnego i niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Rozlanie wzmożona aktywność metaboliczna w topografii ścian żołądka i XII-icy, SUV max do 4,8 - w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Niewielkie pogrubienie trzonu nadnercza prawego oraz nieco większe lewego. Nieliczne drobne węzły chłonne przyaortalne. Drobne zwapnienie w lewym płacie niepowiększonej prostaty.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Masywne osteofity na przednich krawędziach trzonów kręgowych C3 i C4. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa - ciasna na poziomie L5/S1. Os sacrum arcuatum. Drobne zmiany wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i wydatniejsze w stawach żebrowo-poprzecznych.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax 1,8; Prawy płat wątroby SUVmax do 3,2.</t>
+          <t>87</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Rozlanie wzmożony metabolizm FDG w topografii przedniej części dna jamy ustnej/języka, SUV max do 12,9 - do kontroli miejscowej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Nieaktywne metabolicznie węzły chłonne szyjne po stronie lewej wielkości do 14x10mm [największe nadobojczykowe]. Polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej, wielkości 17mm.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Miernie pobudzone metabolicznie pojedyncze i spakietowane węzły chłonne pachowe i międzypiersiowe lewe, wielkości do 34x25mm, SUV max do 1,9 Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne pachowe prawe, wielkości do 10mm Węzły chłonne podobojczykowe wielkości do 11mm. Węzły chłonne podostrogowe wielkości do 12mm. Niewielki obszar zmian miąższowo-włóknistych w segm. 4 płuca lewego. Gorsze upowietrznienie miąższu płucnego i niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Rozlanie wzmożona aktywność metaboliczna w topografii ścian żołądka i XII-icy, SUV max do 4,8 - w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Niewielkie pogrubienie trzonu nadnercza prawego oraz nieco większe lewego. Nieliczne drobne węzły chłonne przyaortalne. Drobne zwapnienie w lewym płacie niepowiększonej prostaty.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Masywne osteofity na przednich krawędziach trzonów kręgowych C3 i C4. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa - ciasna na poziomie L5/S1. Os sacrum arcuatum. Drobne zmiany wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i wydatniejsze w stawach żebrowo-poprzecznych.  Inne: Miażdżyca aorty i tętnic potomnych.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono dobrą odpowiedź metaboliczną choroby chłoniakowej na stosowane leczenie z częściową regresją radiologiczną zmian.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>12.9</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57 min od podania 18F-FDG. Glikemia: 120 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Wzmożony metabolizm FDG w topografii nosogardła SUV max do 3,6 oraz w przedniej części prawego fałdu głosowego SUV max do 3,6- do kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja lewej zatoki czołowej. Wydatne zgrubienia błony śluzowej w sitowiu tylnym, lewym. Polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej, wielkości 20mm.  Klatka piersiowa i śródpiersie: Miernie pobudzone metabolicznie węzły chłonne pachowe lewe wielkości do 23x20 mm SUV max do 1,8. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne podostrogowe wielkości do 13 mm. Niewielki obszar zmian miąższowo-włóknistych w segm. 4 płuca lewego. Gorsze upowietrznienie miąższu płucnego i niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Aktywny metabolicznie węzeł chłonny  okołoaortalny prawy  na poziomie kręgu L1 średnicy 13 mm SUV max 4,1 [Im fuz. 172]. Rozlanie wzmożony metabolizm FDG w żołądku SUV max do 4,0- w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Niewielkie pogrubienie trzonu nadnercza prawego oraz nieco większe lewego. Drobne zwapnienie w lewym płacie niepowiększonej prostaty.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Masywne osteofity na przednich krawędziach trzonów kręgowych C3 i C4. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa - ciasna na poziomie L5/S1 [ze sklerotyczną przebudową blaszek granicznych i przyległych części trzonów kręgowych - typu Modic 3]. Os sacrum arcuatum. Drobne zmiany wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i wydatniejsze w stawach żebrowo-poprzecznych. Ok. 5mm wyspa kostna w głowie prawej kości udowej.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax 1,2 Prawy płat wątroby SUVmax do 2,6</t>
+          <t>120</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Wzmożony metabolizm FDG w topografii nosogardła SUV max do 3,6 oraz w przedniej części prawego fałdu głosowego SUV max do 3,6- do kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja lewej zatoki czołowej. Wydatne zgrubienia błony śluzowej w sitowiu tylnym, lewym. Polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej, wielkości 20mm.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Miernie pobudzone metabolicznie węzły chłonne pachowe lewe wielkości do 23x20 mm SUV max do 1,8. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne podostrogowe wielkości do 13 mm. Niewielki obszar zmian miąższowo-włóknistych w segm. 4 płuca lewego. Gorsze upowietrznienie miąższu płucnego i niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie węzeł chłonny  okołoaortalny prawy  na poziomie kręgu L1 średnicy 13 mm SUV max 4,1 [Im fuz. 172]. Rozlanie wzmożony metabolizm FDG w żołądku SUV max do 4,0- w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Niewielkie pogrubienie trzonu nadnercza prawego oraz nieco większe lewego. Drobne zwapnienie w lewym płacie niepowiększonej prostaty.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Masywne osteofity na przednich krawędziach trzonów kręgowych C3 i C4. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa - ciasna na poziomie L5/S1 [ze sklerotyczną przebudową blaszek granicznych i przyległych części trzonów kręgowych - typu Modic 3]. Os sacrum arcuatum. Drobne zmiany wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i wydatniejsze w stawach żebrowo-poprzecznych. Ok. 5mm wyspa kostna w głowie prawej kości udowej.  Inne: Miażdżyca aorty i tętnic potomnych.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność pojedynczego aktywnego metabolicznie węzła chłonnego okołoaortalnego prawego na poziomie L1- wznowa choroby chłoniakowej (lokalizacja węzła jak w PET/CT wyjściowym z 24.05.2021). Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>4.1</v>
       </c>
     </row>
@@ -568,20 +668,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57 min od podania 18F-FDG. Glikemia: 105mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>: Wzmożony metabolizm FDG w topografii nosogardła SUV max do 3,6 oraz w przedniej części prawego fałdu głosowego SUV max do 3,6- do kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja lewej zatoki czołowej. Polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej, wielkości 16mm. Miernie powiększona tarczyca, zwłaszcza w zakresie prawego płata - do kontroli w USG.  Klatka piersiowa i śródpiersie: Miernie pobudzone metabolicznie węzły chłonne pachowe lewe, drobne prawe wielkości do 15 mm SUV max do 1,5. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne podostrogowe i przytchawicze dolne prawe wielkości do 13 mm. Drobne obwodowe pęcherze rozedmowe w płacie górnym płuca prawego. Gorsze upowietrznienie miąższu płucnego i niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Aktywny metabolicznie węzeł chłonny okołoaortalny prawy  na poziomie kręgu L1 wielkości 31x25 mm SUV max 6,7 [Im fuz. 169]. Pobudzenie metaboliczne w żołądku - w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Niewielkie pogrubienie trzonu nadnercza prawego oraz nieco większe lewego - do 17mm. Drobne zwapnienie w lewym płacie niepowiększonej prostaty. Niewielkie wodniaki obu jąder.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Masywne osteofity na przednich krawędziach trzonów kręgowych C3 i C4. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa - ciasna na poziomie L5/S1 [ze sklerotyczną przebudową blaszek granicznych i przyległych części trzonów kręgowych - typu Modic 3]. Os sacrum arcuatum. Drobne zmiany wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i wydatniejsze w stawach żebrowo-poprzecznych. Ok. 5mm wyspa kostna w głowie prawej kości udowej.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax 1,5; Prawy płat wątroby SUVmax do 2,0.</t>
+          <t>105</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Wzmożony metabolizm FDG w topografii nosogardła SUV max do 3,6 oraz w przedniej części prawego fałdu głosowego SUV max do 3,6- do kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja lewej zatoki czołowej. Polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej, wielkości 16mm. Miernie powiększona tarczyca, zwłaszcza w zakresie prawego płata - do kontroli w USG.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Miernie pobudzone metabolicznie węzły chłonne pachowe lewe, drobne prawe wielkości do 15 mm SUV max do 1,5. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne podostrogowe i przytchawicze dolne prawe wielkości do 13 mm. Drobne obwodowe pęcherze rozedmowe w płacie górnym płuca prawego. Gorsze upowietrznienie miąższu płucnego i niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie węzeł chłonny okołoaortalny prawy  na poziomie kręgu L1 wielkości 31x25 mm SUV max 6,7 [Im fuz. 169]. Pobudzenie metaboliczne w żołądku - w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Niewielkie pogrubienie trzonu nadnercza prawego oraz nieco większe lewego - do 17mm. Drobne zwapnienie w lewym płacie niepowiększonej prostaty. Niewielkie wodniaki obu jąder.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Masywne osteofity na przednich krawędziach trzonów kręgowych C3 i C4. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa - ciasna na poziomie L5/S1 [ze sklerotyczną przebudową blaszek granicznych i przyległych części trzonów kręgowych - typu Modic 3]. Os sacrum arcuatum. Drobne zmiany wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i wydatniejsze w stawach żebrowo-poprzecznych. Ok. 5mm wyspa kostna w głowie prawej kości udowej.  Inne: Miażdżyca aorty i tętnic potomnych.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność pojedynczego aktywnego metabolicznie węzła chłonnego okołoaortalnego prawego na poziomie L1- wznowa choroby chłoniakowej - w porównaniu do badania z 17.02.2022 progresja. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="L5" t="n">
         <v>6.7</v>
       </c>
     </row>
@@ -601,20 +726,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57 min od podania 18F-FDG. Glikemia: 92mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>: Wzmożony metabolizm FDG w topografii przedniej części podniebienia oraz nieco nosogardła i przedniej części prawego fałdu głosowego, SUV max do 3,9- do ew. kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja lewej zatoki czołowej. Polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej, wielkości 16mm. Miernie powiększona tarczyca, zwłaszcza w zakresie prawego płata - do kontroli w USG.  Klatka piersiowa i śródpiersie: Miernie pobudzone metabolicznie węzły chłonne pachowe lewe,  wielkości do 16x13 mm, SUV max do 1,6 oraz drobne prawe. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne podostrogowe i przytchawicze dolne prawe wielkości do 12 mm. Drobne obwodowe pęcherze rozedmowe w płacie górnym płuca prawego. Niewielkie zmiany miąższowe nadprzeponowo po stronie lewej. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Aktywny metabolicznie węzeł chłonny okołoaortalny prawy,  na poziomie kręgu L1 wielkości 34x28 mm SUV max 8,1 [Im fuz. 172]. Pobudzenie metaboliczne w żołądku oraz okrężnicy zstępującej  - w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Niewielkie pogrubienie trzonów obu nadnerczy. Drobne zwapnienie w lewym płacie niepowiększonej prostaty. Niewielkie wodniaki obu jąder.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Masywne osteofity na przednich krawędziach trzonów kręgowych C3 i C4. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa - ciasna na poziomie L5/S1 [ze sklerotyczną przebudową blaszek granicznych i przyległych części trzonów kręgowych - typu Modic 3]. Os sacrum arcuatum. Drobne zmiany wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i wydatniejsze w stawach żebrowo-poprzecznych. Ok. 5mm wyspa kostna w głowie prawej kości udowej.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax 2,0; Prawy płat wątroby SUVmax do 2,6.</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Wzmożony metabolizm FDG w topografii przedniej części podniebienia oraz nieco nosogardła i przedniej części prawego fałdu głosowego, SUV max do 3,9- do ew. kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja lewej zatoki czołowej. Polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej, wielkości 16mm. Miernie powiększona tarczyca, zwłaszcza w zakresie prawego płata - do kontroli w USG.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Miernie pobudzone metabolicznie węzły chłonne pachowe lewe,  wielkości do 16x13 mm, SUV max do 1,6 oraz drobne prawe. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne podostrogowe i przytchawicze dolne prawe wielkości do 12 mm. Drobne obwodowe pęcherze rozedmowe w płacie górnym płuca prawego. Niewielkie zmiany miąższowe nadprzeponowo po stronie lewej. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie węzeł chłonny okołoaortalny prawy,  na poziomie kręgu L1 wielkości 34x28 mm SUV max 8,1 [Im fuz. 172]. Pobudzenie metaboliczne w żołądku oraz okrężnicy zstępującej  - w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Niewielkie pogrubienie trzonów obu nadnerczy. Drobne zwapnienie w lewym płacie niepowiększonej prostaty. Niewielkie wodniaki obu jąder.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Masywne osteofity na przednich krawędziach trzonów kręgowych C3 i C4. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa - ciasna na poziomie L5/S1 [ze sklerotyczną przebudową blaszek granicznych i przyległych części trzonów kręgowych - typu Modic 3]. Os sacrum arcuatum. Drobne zmiany wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i wydatniejsze w stawach żebrowo-poprzecznych. Ok. 5mm wyspa kostna w głowie prawej kości udowej.  Inne: Miażdżyca aorty i tętnic potomnych.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność pojedynczego aktywnego metabolicznie węzła chłonnego okołoaortalnego prawego na poziomie L1- wznowa choroby chłoniakowej - w porównaniu do badania z 12.05.2022 dalsza progresja wielkości. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="L6" t="n">
         <v>8.1</v>
       </c>
     </row>
@@ -634,20 +784,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  56 min od podania 18F-FDG. Glikemia: 125mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>: Wzmożony metabolizm FDG w topografii przedniej części podniebienia oraz nieco nosogardła i przedniej części prawego fałdu głosowego, SUV max do 3,8- do ew. kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja lewej zatoki czołowej. Polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej, wielkości 16mm. Miernie powiększona tarczyca, zwłaszcza w zakresie prawego płata - do kontroli w USG.  Klatka piersiowa i śródpiersie: Miernie pobudzone metabolicznie węzły chłonne pachowe lewe,  wielkości do 16x13 mm, SUV max do 1,4 oraz drobne prawe. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne podostrogowe i przytchawicze dolne prawe wielkości do 12 mm. Drobne obwodowe pęcherze rozedmowe w płacie górnym płuca prawego. Niewielkie zmiany miąższowe nadprzeponowo po stronie lewej. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Aktywny metabolicznie węzeł chłonny okołoaortalny prawy, na poziomie kręgu L1 wielkości 37x28 mm (poprzednio 34x28 mm) SUV max 6,0 (poprzednio SUV max 8,1) [Im fuz. 177]. Pobudzenie metaboliczne w żołądku oraz okrężnicy zstępującej  - w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Niewielkie pogrubienie trzonów obu nadnerczy. Drobne zwapnienie w lewym płacie niepowiększonej prostaty. Niewielkie wodniaki obu jąder.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Masywne osteofity na przednich krawędziach trzonów kręgowych C3 i C4. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa - ciasna na poziomie L5/S1 [ze sklerotyczną przebudową blaszek granicznych i przyległych części trzonów kręgowych - typu Modic 3]. Os sacrum arcuatum. Drobne zmiany wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i wydatniejsze w stawach żebrowo-poprzecznych. Ok. 5mm wyspa kostna w głowie prawej kości udowej.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax 2,0; Prawy płat wątroby SUVmax do 2,4.</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Wzmożony metabolizm FDG w topografii przedniej części podniebienia oraz nieco nosogardła i przedniej części prawego fałdu głosowego, SUV max do 3,8- do ew. kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja lewej zatoki czołowej. Polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej, wielkości 16mm. Miernie powiększona tarczyca, zwłaszcza w zakresie prawego płata - do kontroli w USG.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Miernie pobudzone metabolicznie węzły chłonne pachowe lewe,  wielkości do 16x13 mm, SUV max do 1,4 oraz drobne prawe. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne podostrogowe i przytchawicze dolne prawe wielkości do 12 mm. Drobne obwodowe pęcherze rozedmowe w płacie górnym płuca prawego. Niewielkie zmiany miąższowe nadprzeponowo po stronie lewej. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie węzeł chłonny okołoaortalny prawy, na poziomie kręgu L1 wielkości 37x28 mm (poprzednio 34x28 mm) SUV max 6,0 (poprzednio SUV max 8,1) [Im fuz. 177]. Pobudzenie metaboliczne w żołądku oraz okrężnicy zstępującej  - w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Niewielkie pogrubienie trzonów obu nadnerczy. Drobne zwapnienie w lewym płacie niepowiększonej prostaty. Niewielkie wodniaki obu jąder.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Masywne osteofity na przednich krawędziach trzonów kręgowych C3 i C4. Wielopoziomowo dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa - ciasna na poziomie L5/S1 [ze sklerotyczną przebudową blaszek granicznych i przyległych części trzonów kręgowych - typu Modic 3]. Os sacrum arcuatum. Drobne zmiany wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i wydatniejsze w stawach żebrowo-poprzecznych. Ok. 5mm wyspa kostna w głowie prawej kości udowej.  Inne: Miażdżyca aorty i tętnic potomnych.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność pojedynczego aktywnego metabolicznie węzła chłonnego okołoaortalnego prawego na poziomie L1- wznowa choroby chłoniakowej - w porównaniu do badania z 17.10.2022 obraz PET/CT z 18F-FDG nie uległ zasadniczej zmianie. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="L7" t="n">
         <v>8.1</v>
       </c>
     </row>
